--- a/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora pricing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 ejemplos validados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Calculadora pricing'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'10 ejemplos validados'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -531,7 +534,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -557,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -711,6 +715,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -726,7 +731,7 @@
       </c>
       <c r="B16" s="7">
         <f>IF(B5="B2B", IF(B6&lt;40, 22, IF(B6&lt;80, 19, 17)), IF(B6&lt;40, 25, IF(B6&lt;80, 21, 18)))</f>
-        <v/>
+        <v>17.0</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
@@ -742,7 +747,7 @@
       </c>
       <c r="B17" s="9">
         <f>IF(OR(B8="Marisco",B8="Negro"),1.25,IF(OR(B8="Banda",B8="Senyoret"),1.18,IF(B8="Valenciana",1.10,1.00)))</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -758,7 +763,7 @@
       </c>
       <c r="B18" s="9">
         <f>IF(B9="sí", 1.18, 1.00)</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
@@ -774,7 +779,7 @@
       </c>
       <c r="B19" s="9">
         <f>IF(B11="sí", 1.08, 1.00)</f>
-        <v/>
+        <v>1.08</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -790,7 +795,7 @@
       </c>
       <c r="B20" s="9">
         <f>IF(B13="lluvia", 1.04, 1.00)</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -806,7 +811,7 @@
       </c>
       <c r="B21" s="9">
         <f>IF(B12="sí", 0.94, 1.00)</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -822,7 +827,7 @@
       </c>
       <c r="B22" s="7">
         <f>B7*0.95*2</f>
-        <v/>
+        <v>66.5</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -838,7 +843,7 @@
       </c>
       <c r="B23" s="7">
         <f>B10*120</f>
-        <v/>
+        <v>120.0</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -846,6 +851,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -861,7 +867,7 @@
       </c>
       <c r="B26" s="11">
         <f>B16*B17*B18*B19*B20*B21</f>
-        <v/>
+        <v>18.36</v>
       </c>
     </row>
     <row r="27">
@@ -872,7 +878,7 @@
       </c>
       <c r="B27" s="11">
         <f>B26*B6</f>
-        <v/>
+        <v>1468.8</v>
       </c>
     </row>
     <row r="28">
@@ -883,7 +889,7 @@
       </c>
       <c r="B28" s="11">
         <f>B22+B23</f>
-        <v/>
+        <v>186.5</v>
       </c>
     </row>
     <row r="29">
@@ -894,7 +900,7 @@
       </c>
       <c r="B29" s="12">
         <f>B27+B28</f>
-        <v/>
+        <v>1655.3</v>
       </c>
     </row>
     <row r="30">
@@ -905,7 +911,7 @@
       </c>
       <c r="B30" s="11">
         <f>B29/B6</f>
-        <v/>
+        <v>20.69125</v>
       </c>
     </row>
     <row r="31">
@@ -916,7 +922,7 @@
       </c>
       <c r="B31" s="13">
         <f>B29*0.3</f>
-        <v/>
+        <v>496.59</v>
       </c>
     </row>
     <row r="32">
@@ -927,7 +933,7 @@
       </c>
       <c r="B32" s="11">
         <f>B29*0.55</f>
-        <v/>
+        <v>910.4150000000001</v>
       </c>
     </row>
     <row r="33">
@@ -942,30 +948,39 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="C12:E12"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C19:E19"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -973,7 +988,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1002,6 +1017,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1366,9 +1382,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>